--- a/Book.xlsx
+++ b/Book.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Svgu library v.2.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{895F9AD0-5E61-4A44-95CC-A2E8FC8F0E1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D773154A-A2CF-4405-BBD7-471050D6E438}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="BookCardReport" sheetId="1" r:id="rId1"/>
+    <sheet name="Book" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="19">
   <si>
     <t>Sondur, Shreya.</t>
   </si>
@@ -442,16 +442,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8802DD2-7BA0-4A46-AB48-F63399F32449}">
   <dimension ref="A1:G28"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
-  <cols>
-    <col min="1" max="1" width="44.109375" customWidth="1"/>
-    <col min="2" max="2" width="0" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="26.6640625" customWidth="1"/>
-    <col min="4" max="4" width="14.109375" customWidth="1"/>
-    <col min="7" max="7" width="10.5546875" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="2" t="s">
@@ -473,7 +466,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15.75" customHeight="1">
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -493,7 +486,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15.75" customHeight="1">
+    <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -513,7 +506,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15.75" customHeight="1">
+    <row r="4" spans="1:7">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -533,7 +526,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15.75" customHeight="1">
+    <row r="5" spans="1:7">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -553,7 +546,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15.75" customHeight="1">
+    <row r="6" spans="1:7">
       <c r="A6" s="1" t="s">
         <v>3</v>
       </c>
@@ -573,7 +566,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15.75" customHeight="1">
+    <row r="7" spans="1:7">
       <c r="A7" s="1" t="s">
         <v>2</v>
       </c>
@@ -593,7 +586,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="15.75" customHeight="1">
+    <row r="8" spans="1:7">
       <c r="A8" s="1" t="s">
         <v>2</v>
       </c>
@@ -613,7 +606,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15.75" customHeight="1">
+    <row r="9" spans="1:7">
       <c r="A9" s="1" t="s">
         <v>2</v>
       </c>
@@ -633,7 +626,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15.75" customHeight="1">
+    <row r="10" spans="1:7">
       <c r="A10" s="1" t="s">
         <v>2</v>
       </c>
@@ -653,7 +646,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="15.75" customHeight="1">
+    <row r="11" spans="1:7">
       <c r="A11" s="1" t="s">
         <v>2</v>
       </c>
@@ -673,7 +666,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="15.75" customHeight="1">
+    <row r="12" spans="1:7">
       <c r="A12" s="1" t="s">
         <v>6</v>
       </c>
@@ -693,7 +686,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="15.75" customHeight="1">
+    <row r="13" spans="1:7">
       <c r="A13" s="1" t="s">
         <v>6</v>
       </c>
@@ -713,7 +706,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="15.75" customHeight="1">
+    <row r="14" spans="1:7">
       <c r="A14" s="1" t="s">
         <v>6</v>
       </c>
@@ -733,7 +726,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="15.75" customHeight="1">
+    <row r="15" spans="1:7">
       <c r="A15" s="1" t="s">
         <v>6</v>
       </c>
@@ -753,7 +746,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="15.75" customHeight="1">
+    <row r="16" spans="1:7">
       <c r="A16" s="1" t="s">
         <v>6</v>
       </c>
@@ -773,7 +766,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="15.75" customHeight="1">
+    <row r="17" spans="1:7">
       <c r="A17" s="1" t="s">
         <v>9</v>
       </c>
@@ -793,7 +786,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="15.75" customHeight="1">
+    <row r="18" spans="1:7">
       <c r="A18" s="1" t="s">
         <v>9</v>
       </c>
@@ -813,7 +806,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="0" hidden="1" customHeight="1">
+    <row r="19" spans="1:7">
       <c r="A19" s="1" t="s">
         <v>9</v>
       </c>
@@ -826,8 +819,14 @@
       <c r="E19" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" ht="0" hidden="1" customHeight="1">
+      <c r="F19">
+        <v>2194</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="A20" s="1" t="s">
         <v>9</v>
       </c>
@@ -839,6 +838,12 @@
       </c>
       <c r="E20" s="2" t="s">
         <v>11</v>
+      </c>
+      <c r="F20">
+        <v>2195</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1002,8 +1007,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.14000000000000001" right="0.14000000000000001" top="0.433" bottom="0.433" header="0.433" footer="0.433"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
-  <headerFooter alignWithMargins="0"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Book.xlsx
+++ b/Book.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Svgu library v.2.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D773154A-A2CF-4405-BBD7-471050D6E438}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{079F37AA-086F-4BF7-8396-15608A926E54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -443,566 +443,570 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8802DD2-7BA0-4A46-AB48-F63399F32449}">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="52.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.88671875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>15</v>
       </c>
+      <c r="B1" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="C1" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G1" t="s">
+      <c r="F1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B2" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="4">
+      <c r="C2" s="4">
         <v>6.7854580000000002</v>
       </c>
-      <c r="E2" t="s">
+      <c r="D2" t="s">
         <v>1</v>
       </c>
-      <c r="F2">
+      <c r="E2">
         <v>2177</v>
       </c>
-      <c r="G2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+      <c r="F2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C3" t="s">
+      <c r="B3" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="4">
+      <c r="C3" s="4">
         <v>6.7</v>
       </c>
-      <c r="E3" t="s">
+      <c r="D3" t="s">
         <v>1</v>
       </c>
-      <c r="F3">
+      <c r="E3">
         <v>2178</v>
       </c>
-      <c r="G3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+      <c r="F3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4" t="s">
+      <c r="B4" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="4">
+      <c r="C4" s="4">
         <v>6.7</v>
       </c>
-      <c r="E4" t="s">
+      <c r="D4" t="s">
         <v>1</v>
       </c>
-      <c r="F4">
+      <c r="E4">
         <v>2179</v>
       </c>
-      <c r="G4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+      <c r="F4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C5" t="s">
+      <c r="B5" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="4">
+      <c r="C5" s="4">
         <v>6.7</v>
       </c>
-      <c r="E5" t="s">
+      <c r="D5" t="s">
         <v>1</v>
       </c>
-      <c r="F5">
+      <c r="E5">
         <v>2180</v>
       </c>
-      <c r="G5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+      <c r="F5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C6" t="s">
+      <c r="B6" t="s">
         <v>0</v>
       </c>
-      <c r="D6" s="4">
+      <c r="C6" s="4">
         <v>6.7</v>
       </c>
-      <c r="E6" t="s">
+      <c r="D6" t="s">
         <v>1</v>
       </c>
-      <c r="F6">
+      <c r="E6">
         <v>2181</v>
       </c>
-      <c r="G6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+      <c r="F6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C7" t="s">
+      <c r="B7" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="4">
+      <c r="C7" s="4">
         <v>6.7</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F7" s="2">
+      <c r="E7" s="2">
         <v>2182</v>
       </c>
-      <c r="G7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+      <c r="F7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C8" t="s">
+      <c r="B8" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="4">
+      <c r="C8" s="4">
         <v>6.7</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F8" s="2">
+      <c r="E8" s="2">
         <v>2183</v>
       </c>
-      <c r="G8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+      <c r="F8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C9" t="s">
+      <c r="B9" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="4">
+      <c r="C9" s="4">
         <v>6.7</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F9" s="2">
+      <c r="E9" s="2">
         <v>2184</v>
       </c>
-      <c r="G9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+      <c r="F9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C10" t="s">
+      <c r="B10" t="s">
         <v>4</v>
       </c>
-      <c r="D10" s="4">
+      <c r="C10" s="4">
         <v>6.7</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F10" s="2">
+      <c r="E10" s="2">
         <v>2185</v>
       </c>
-      <c r="G10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+      <c r="F10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C11" t="s">
+      <c r="B11" t="s">
         <v>4</v>
       </c>
-      <c r="D11" s="4">
+      <c r="C11" s="4">
         <v>6.7</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F11" s="2">
+      <c r="E11" s="2">
         <v>2186</v>
       </c>
-      <c r="G11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+      <c r="F11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C12" t="s">
+      <c r="B12" t="s">
         <v>7</v>
       </c>
-      <c r="D12">
+      <c r="C12">
         <v>658.5</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="D12" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F12" s="2">
+      <c r="E12" s="2">
         <v>2187</v>
       </c>
-      <c r="G12" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+      <c r="F12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C13" t="s">
+      <c r="B13" t="s">
         <v>7</v>
       </c>
-      <c r="D13">
+      <c r="C13">
         <v>658.5</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="D13" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F13" s="2">
+      <c r="E13" s="2">
         <v>2188</v>
       </c>
-      <c r="G13" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
+      <c r="F13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
       <c r="A14" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C14" t="s">
+      <c r="B14" t="s">
         <v>7</v>
       </c>
-      <c r="D14">
+      <c r="C14">
         <v>658.5</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="D14" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="2">
+      <c r="E14" s="2">
         <v>2189</v>
       </c>
-      <c r="G14" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
+      <c r="F14" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C15" t="s">
+      <c r="B15" t="s">
         <v>7</v>
       </c>
-      <c r="D15">
+      <c r="C15">
         <v>658.5</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="D15" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F15" s="2">
+      <c r="E15" s="2">
         <v>2190</v>
       </c>
-      <c r="G15" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
+      <c r="F15" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C16" t="s">
+      <c r="B16" t="s">
         <v>7</v>
       </c>
-      <c r="D16">
+      <c r="C16">
         <v>658.5</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="D16" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F16" s="2">
+      <c r="E16" s="2">
         <v>2191</v>
       </c>
-      <c r="G16" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
+      <c r="F16" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C17" t="s">
-        <v>10</v>
-      </c>
-      <c r="D17" s="3">
-        <v>5.13</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F17" s="2">
+      <c r="B17" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="3">
+        <v>5.13</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" s="2">
         <v>2192</v>
       </c>
-      <c r="G17" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
+      <c r="F17" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C18" t="s">
-        <v>10</v>
-      </c>
-      <c r="D18" s="3">
-        <v>5.13</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F18" s="2">
+      <c r="B18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="3">
+        <v>5.13</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" s="2">
         <v>2193</v>
       </c>
-      <c r="G18" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
+      <c r="F18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C19" t="s">
-        <v>10</v>
-      </c>
-      <c r="D19" s="3">
-        <v>5.13</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F19">
+      <c r="B19" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="3">
+        <v>5.13</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19">
         <v>2194</v>
       </c>
-      <c r="G19" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
+      <c r="F19" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C20" t="s">
-        <v>10</v>
-      </c>
-      <c r="D20" s="3">
-        <v>5.13</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F20">
+      <c r="B20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="3">
+        <v>5.13</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20">
         <v>2195</v>
       </c>
-      <c r="G20" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
+      <c r="F20" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C21" t="s">
-        <v>10</v>
-      </c>
-      <c r="D21" s="3">
-        <v>5.13</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F21" s="2">
+      <c r="B21" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="3">
+        <v>5.13</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" s="2">
         <v>2194</v>
       </c>
-      <c r="G21" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
+      <c r="F21" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
       <c r="A22" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C22" t="s">
-        <v>10</v>
-      </c>
-      <c r="D22" s="3">
-        <v>5.13</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F22" s="2">
+      <c r="B22" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="3">
+        <v>5.13</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" s="2">
         <v>2195</v>
       </c>
-      <c r="G22" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
+      <c r="F22" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
       <c r="A23" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C23" t="s">
-        <v>10</v>
-      </c>
-      <c r="D23" s="3">
-        <v>5.13</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F23" s="2">
+      <c r="B23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="3">
+        <v>5.13</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" s="2">
         <v>2196</v>
       </c>
-      <c r="G23" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
+      <c r="F23" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
       <c r="A24" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C24" t="s">
-        <v>10</v>
-      </c>
-      <c r="D24" s="3">
-        <v>5.13</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F24">
+      <c r="B24" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="3">
+        <v>5.13</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24">
         <v>2197</v>
       </c>
-      <c r="G24" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
+      <c r="F24" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
       <c r="A25" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C25" t="s">
-        <v>10</v>
-      </c>
-      <c r="D25" s="3">
-        <v>5.13</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F25" s="2">
+      <c r="B25" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="3">
+        <v>5.13</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" s="2">
         <v>2198</v>
       </c>
-      <c r="G25" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
+      <c r="F25" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
       <c r="A26" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C26" t="s">
-        <v>10</v>
-      </c>
-      <c r="D26" s="3">
-        <v>5.13</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F26" s="2">
+      <c r="B26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="3">
+        <v>5.13</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" s="2">
         <v>2199</v>
       </c>
-      <c r="G26" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
+      <c r="F26" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
       <c r="A27" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C27" t="s">
-        <v>10</v>
-      </c>
-      <c r="D27" s="3">
-        <v>5.13</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F27" s="2">
+      <c r="B27" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="3">
+        <v>5.13</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" s="2">
         <v>2200</v>
       </c>
-      <c r="G27" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
+      <c r="F27" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
       <c r="A28" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C28" t="s">
-        <v>10</v>
-      </c>
-      <c r="D28" s="3">
-        <v>5.13</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F28" s="2">
+      <c r="B28" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="3">
+        <v>5.13</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28" s="2">
         <v>2201</v>
       </c>
-      <c r="G28" t="s">
+      <c r="F28" t="s">
         <v>18</v>
       </c>
     </row>
